--- a/business_forms/007_aft_submission_form--business_forms.xlsx
+++ b/business_forms/007_aft_submission_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,8 +973,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'new_aft_setup',_'value':_'new_setup'}</t>
+          <t>new_aft_setup</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'New AFT Setup', 'value': 'new_setup'}</t>
+          <t>New AFT Setup</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'modification_to_existing_aft',_'value':_'modification'}</t>
+          <t>modification_to_existing_aft</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Modification to Existing AFT', 'value': 'modification'}</t>
+          <t>Modification to Existing AFT</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'cancellation',_'value':_'cancellation'}</t>
+          <t>cancellation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Cancellation', 'value': 'cancellation'}</t>
+          <t>Cancellation</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'status_inquiry',_'value':_'inquiry'}</t>
+          <t>status_inquiry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Status Inquiry', 'value': 'inquiry'}</t>
+          <t>Status Inquiry</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'usd_-_us_dollar',_'value':_'usd'}</t>
+          <t>usd_-_us_dollar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'USD - US Dollar', 'value': 'usd'}</t>
+          <t>USD - US Dollar</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'eur_-_euro',_'value':_'eur'}</t>
+          <t>eur_-_euro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'EUR - Euro', 'value': 'eur'}</t>
+          <t>EUR - Euro</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'gbp_-_british_pound',_'value':_'gbp'}</t>
+          <t>gbp_-_british_pound</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'GBP - British Pound', 'value': 'gbp'}</t>
+          <t>GBP - British Pound</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'cad_-_canadian_dollar',_'value':_'cad'}</t>
+          <t>cad_-_canadian_dollar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'CAD - Canadian Dollar', 'value': 'cad'}</t>
+          <t>CAD - Canadian Dollar</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'one-time',_'value':_'one_time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'One-time', 'value': 'one_time'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly', 'value': 'quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Annually', 'value': 'annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'authorization_form',_'value':_'authorization'}</t>
+          <t>authorization_form</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Authorization Form', 'value': 'authorization'}</t>
+          <t>Authorization Form</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'voided_check',_'value':_'voided_check'}</t>
+          <t>voided_check</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Voided Check', 'value': 'voided_check'}</t>
+          <t>Voided Check</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'contract/agreement',_'value':_'contract'}</t>
+          <t>contract/agreement</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Contract/Agreement', 'value': 'contract'}</t>
+          <t>Contract/Agreement</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'invoice',_'value':_'invoice'}</t>
+          <t>invoice</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Invoice', 'value': 'invoice'}</t>
+          <t>Invoice</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'tax_documentation',_'value':_'tax_doc'}</t>
+          <t>tax_documentation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Tax Documentation', 'value': 'tax_doc'}</t>
+          <t>Tax Documentation</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'normal',_'value':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Normal', 'value': 'normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'high_(requires_justification)',_'value':_'high'}</t>
+          <t>high_(requires_justification)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'High (Requires justification)', 'value': 'high'}</t>
+          <t>High (Requires justification)</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'urgent/immediate',_'value':_'urgent'}</t>
+          <t>urgent/immediate</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Urgent/Immediate', 'value': 'urgent'}</t>
+          <t>Urgent/Immediate</t>
         </is>
       </c>
     </row>
